--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N31_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>97.74214431428882</v>
       </c>
       <c r="E2" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F2" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>33.70180341679748</v>
       </c>
       <c r="E3" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F3" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>5.568694255538786</v>
       </c>
       <c r="E4" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F4" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>5.022953738974969</v>
       </c>
       <c r="E5" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F5" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>21.08715515315888</v>
       </c>
       <c r="E6" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F6" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.25545524854526</v>
+        <v>31.31445384640409</v>
       </c>
       <c r="D7" t="n">
-        <v>18.1758166806213</v>
+        <v>31.33667675178497</v>
       </c>
       <c r="E7" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F7" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.341492676308434</v>
+        <v>18.25545524854526</v>
       </c>
       <c r="D8" t="n">
-        <v>6.541604677924533</v>
+        <v>18.1758166806213</v>
       </c>
       <c r="E8" t="n">
-        <v>28.53199922119799</v>
+        <v>26.936026960712</v>
       </c>
       <c r="F8" t="n">
-        <v>28.55839597297312</v>
+        <v>26.95935546288829</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,23 +704,55 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
+        <v>6.341492676308434</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.541604677924533</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.936026960712</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.95935546288829</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W0029F0002T0006Z000C1N31.png</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
         <v>28.36988294364973</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>28.27556049133944</v>
       </c>
-      <c r="E9" t="n">
-        <v>28.53199922119799</v>
-      </c>
-      <c r="F9" t="n">
-        <v>28.55839597297312</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>T7604</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" t="n">
+        <v>26.936026960712</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26.95935546288829</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.50879098006826</v>
+        <v>15.84517853426109</v>
       </c>
       <c r="D2" t="n">
-        <v>97.74214431428882</v>
+        <v>15.88309845107193</v>
       </c>
       <c r="E2" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F2" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.38801125125589</v>
+        <v>5.425551828329082</v>
       </c>
       <c r="D3" t="n">
-        <v>33.70180341679748</v>
+        <v>5.476543055229591</v>
       </c>
       <c r="E3" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F3" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.462637015235468</v>
+        <v>0.8876785149757636</v>
       </c>
       <c r="D4" t="n">
-        <v>5.568694255538786</v>
+        <v>0.9049128165250528</v>
       </c>
       <c r="E4" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F4" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.703272492824981</v>
+        <v>0.7642817800840594</v>
       </c>
       <c r="D5" t="n">
-        <v>5.022953738974969</v>
+        <v>0.8162299825834326</v>
       </c>
       <c r="E5" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F5" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.14603785476263</v>
+        <v>3.436231151398928</v>
       </c>
       <c r="D6" t="n">
-        <v>21.08715515315888</v>
+        <v>3.426662712388318</v>
       </c>
       <c r="E6" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F6" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.31445384640409</v>
+        <v>5.088598750040665</v>
       </c>
       <c r="D7" t="n">
-        <v>31.33667675178497</v>
+        <v>5.092209972165057</v>
       </c>
       <c r="E7" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F7" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.25545524854526</v>
+        <v>2.966511477888605</v>
       </c>
       <c r="D8" t="n">
-        <v>18.1758166806213</v>
+        <v>2.953570210600961</v>
       </c>
       <c r="E8" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F8" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.341492676308434</v>
+        <v>1.03049255990012</v>
       </c>
       <c r="D9" t="n">
-        <v>6.541604677924533</v>
+        <v>1.063010760162737</v>
       </c>
       <c r="E9" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F9" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.36988294364973</v>
+        <v>4.610105978343082</v>
       </c>
       <c r="D10" t="n">
-        <v>28.27556049133944</v>
+        <v>4.594778579842659</v>
       </c>
       <c r="E10" t="n">
-        <v>26.936026960712</v>
+        <v>4.3771043811157</v>
       </c>
       <c r="F10" t="n">
-        <v>26.95935546288829</v>
+        <v>4.380895262719347</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
